--- a/OCT_2026/10-20-26/Rainbow Key_Account.xlsx
+++ b/OCT_2026/10-20-26/Rainbow Key_Account.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B69D658-403C-48FC-B8DC-0F95B280330C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53F4C8F-8753-429B-A260-CE625C32C798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dist Price List (2)" sheetId="41" state="hidden" r:id="rId1"/>
@@ -47558,7 +47558,7 @@
       <c r="L4" s="391"/>
       <c r="M4" s="394">
         <f ca="1">TODAY()+1</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="N4" s="394"/>
       <c r="O4" s="394"/>
@@ -47586,7 +47586,7 @@
       <c r="L5" s="391"/>
       <c r="M5" s="394">
         <f ca="1">M4-1</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="N5" s="390"/>
       <c r="O5" s="390"/>
@@ -53801,7 +53801,7 @@
       </c>
       <c r="T3" s="301">
         <f>+'1'!P35</f>
-        <v>22043.047496186442</v>
+        <v>0</v>
       </c>
       <c r="XEW3" t="s">
         <v>80</v>
@@ -53823,7 +53823,7 @@
       </c>
       <c r="T4" s="301">
         <f>+'2'!P35</f>
-        <v>4277.0240656779661</v>
+        <v>0</v>
       </c>
       <c r="XEX4" t="s">
         <v>105</v>
@@ -53877,7 +53877,7 @@
       </c>
       <c r="T5" s="301">
         <f>+'3'!P35</f>
-        <v>10199.031875847457</v>
+        <v>0</v>
       </c>
       <c r="XEX5" t="s">
         <v>106</v>
@@ -53966,19 +53966,19 @@
       </c>
       <c r="H7" s="286">
         <f>+'1'!H16+'2'!H16+'3'!H16+'4'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16+'17'!H16+'18'!H16+'19'!H16+'20'!H16+'21'!H16+'22'!H16+'23'!H16+'24'!H16+'25'!H16+'26'!H16+'27'!H16+'28'!H16+'29'!H16+'30'!H16</f>
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="I7" s="235">
         <f>(G7*D7)*F7+H7*F7</f>
-        <v>6925.05</v>
+        <v>4826.55</v>
       </c>
       <c r="J7" s="286">
         <f>+'1'!J16+'2'!J16+'3'!J16+'4'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16+'19'!J16+'20'!J16+'21'!J16+'22'!J16+'23'!J16+'24'!J16+'25'!J16+'26'!J16+'27'!J16+'28'!J16+'29'!J16+'30'!J16</f>
-        <v>969.50700000000006</v>
+        <v>675.7170000000001</v>
       </c>
       <c r="K7" s="286">
         <f>+'1'!K16+'2'!K16+'3'!K16+'4'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16+'11'!K16+'12'!K16+'13'!K16+'14'!K16+'15'!K16+'16'!K16+'17'!K16+'18'!K16+'19'!K16+'20'!K16+'21'!K16+'22'!K16+'23'!K16+'24'!K16+'25'!K16+'26'!K16+'27'!K16+'28'!K16+'29'!K16+'30'!K16</f>
-        <v>242.37675000000002</v>
+        <v>168.92925000000002</v>
       </c>
       <c r="L7" s="286">
         <f>+'1'!L16+'2'!L16+'3'!L16+'4'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16+'11'!L16+'12'!L16+'13'!L16+'14'!L16+'15'!L16+'16'!L16+'17'!L16+'18'!L16+'19'!L16+'20'!L16+'21'!L16+'22'!L16+'23'!L16+'24'!L16+'25'!L16+'26'!L16+'27'!L16+'28'!L16+'29'!L16+'30'!L16</f>
@@ -53986,19 +53986,19 @@
       </c>
       <c r="M7" s="229">
         <f>I7-SUM(J7:L7)</f>
-        <v>5713.1662500000002</v>
+        <v>3981.9037499999999</v>
       </c>
       <c r="N7" s="286">
         <f>+'1'!N16+'2'!N16+'3'!N16+'4'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16+'11'!N16+'12'!N16+'13'!N16+'14'!N16+'15'!N16+'16'!N16+'17'!N16+'18'!N16+'19'!N16+'20'!N16+'21'!N16+'22'!N16+'23'!N16+'24'!N16+'25'!N16+'26'!N16+'27'!N16+'28'!N16+'29'!N16+'30'!N16</f>
-        <v>1308.8135593220334</v>
+        <v>912.20338983050806</v>
       </c>
       <c r="O7" s="286">
         <f>+'1'!O16+'2'!O16+'3'!O16+'4'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16+'11'!O16+'12'!O16+'13'!O16+'14'!O16+'15'!O16+'16'!O16+'17'!O16+'18'!O16+'19'!O16+'20'!O16+'21'!O16+'22'!O16+'23'!O16+'24'!O16+'25'!O16+'26'!O16+'27'!O16+'28'!O16+'29'!O16+'30'!O16</f>
-        <v>35.109899046610167</v>
+        <v>24.470535699152542</v>
       </c>
       <c r="P7" s="118">
         <f>M7+N7+O7</f>
-        <v>7057.0897083686432</v>
+        <v>4918.5776755296611</v>
       </c>
       <c r="Q7" s="142"/>
       <c r="R7" s="299">
@@ -54125,19 +54125,19 @@
       </c>
       <c r="H9" s="286">
         <f>+'1'!H18+'2'!H18+'3'!H18+'4'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18+'17'!H18+'18'!H18+'19'!H18+'20'!H18+'21'!H18+'22'!H18+'23'!H18+'24'!H18+'25'!H18+'26'!H18+'27'!H18+'28'!H18+'29'!H18+'30'!H18</f>
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="I9" s="236">
         <f t="shared" si="0"/>
-        <v>14532.112499999999</v>
+        <v>4039.6124999999997</v>
       </c>
       <c r="J9" s="286">
         <f>+'1'!J18+'2'!J18+'3'!J18+'4'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18+'19'!J18+'20'!J18+'21'!J18+'22'!J18+'23'!J18+'24'!J18+'25'!J18+'26'!J18+'27'!J18+'28'!J18+'29'!J18+'30'!J18</f>
-        <v>2034.4957500000003</v>
+        <v>565.54575</v>
       </c>
       <c r="K9" s="286">
         <f>+'1'!K18+'2'!K18+'3'!K18+'4'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18+'11'!K18+'12'!K18+'13'!K18+'14'!K18+'15'!K18+'16'!K18+'17'!K18+'18'!K18+'19'!K18+'20'!K18+'21'!K18+'22'!K18+'23'!K18+'24'!K18+'25'!K18+'26'!K18+'27'!K18+'28'!K18+'29'!K18+'30'!K18</f>
-        <v>508.62393750000007</v>
+        <v>141.3864375</v>
       </c>
       <c r="L9" s="286">
         <f>+'1'!L18+'2'!L18+'3'!L18+'4'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18+'11'!L18+'12'!L18+'13'!L18+'14'!L18+'15'!L18+'16'!L18+'17'!L18+'18'!L18+'19'!L18+'20'!L18+'21'!L18+'22'!L18+'23'!L18+'24'!L18+'25'!L18+'26'!L18+'27'!L18+'28'!L18+'29'!L18+'30'!L18</f>
@@ -54145,19 +54145,19 @@
       </c>
       <c r="M9" s="230">
         <f t="shared" si="1"/>
-        <v>11988.992812499999</v>
+        <v>3332.6803124999997</v>
       </c>
       <c r="N9" s="286">
         <f>+'1'!N18+'2'!N18+'3'!N18+'4'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18+'11'!N18+'12'!N18+'13'!N18+'14'!N18+'15'!N18+'16'!N18+'17'!N18+'18'!N18+'19'!N18+'20'!N18+'21'!N18+'22'!N18+'23'!N18+'24'!N18+'25'!N18+'26'!N18+'27'!N18+'28'!N18+'29'!N18+'30'!N18</f>
-        <v>2746.5254237288123</v>
+        <v>763.47457627118615</v>
       </c>
       <c r="O9" s="286">
         <f>+'1'!O18+'2'!O18+'3'!O18+'4'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18+'11'!O18+'12'!O18+'13'!O18+'14'!O18+'15'!O18+'16'!O18+'17'!O18+'18'!O18+'19'!O18+'20'!O18+'21'!O18+'22'!O18+'23'!O18+'24'!O18+'25'!O18+'26'!O18+'27'!O18+'28'!O18+'29'!O18+'30'!O18</f>
-        <v>73.677591181144066</v>
+        <v>20.480774443855928</v>
       </c>
       <c r="P9" s="119">
         <f t="shared" si="2"/>
-        <v>14809.195827409954</v>
+        <v>4116.6356632150419</v>
       </c>
       <c r="R9" s="299">
         <v>7</v>
@@ -54201,19 +54201,19 @@
       </c>
       <c r="H10" s="286">
         <f>+'1'!H19+'2'!H19+'3'!H19+'4'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19+'17'!H19+'18'!H19+'19'!H19+'20'!H19+'21'!H19+'22'!H19+'23'!H19+'24'!H19+'25'!H19+'26'!H19+'27'!H19+'28'!H19+'29'!H19+'30'!H19</f>
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="I10" s="236">
         <f t="shared" si="0"/>
-        <v>11404.48</v>
+        <v>8498.8799999999992</v>
       </c>
       <c r="J10" s="286">
         <f>+'1'!J19+'2'!J19+'3'!J19+'4'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19+'19'!J19+'20'!J19+'21'!J19+'22'!J19+'23'!J19+'24'!J19+'25'!J19+'26'!J19+'27'!J19+'28'!J19+'29'!J19+'30'!J19</f>
-        <v>1596.6272000000004</v>
+        <v>1189.8432000000003</v>
       </c>
       <c r="K10" s="286">
         <f>+'1'!K19+'2'!K19+'3'!K19+'4'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19+'11'!K19+'12'!K19+'13'!K19+'14'!K19+'15'!K19+'16'!K19+'17'!K19+'18'!K19+'19'!K19+'20'!K19+'21'!K19+'22'!K19+'23'!K19+'24'!K19+'25'!K19+'26'!K19+'27'!K19+'28'!K19+'29'!K19+'30'!K19</f>
-        <v>399.15680000000009</v>
+        <v>297.46080000000006</v>
       </c>
       <c r="L10" s="286">
         <f>+'1'!L19+'2'!L19+'3'!L19+'4'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19+'11'!L19+'12'!L19+'13'!L19+'14'!L19+'15'!L19+'16'!L19+'17'!L19+'18'!L19+'19'!L19+'20'!L19+'21'!L19+'22'!L19+'23'!L19+'24'!L19+'25'!L19+'26'!L19+'27'!L19+'28'!L19+'29'!L19+'30'!L19</f>
@@ -54221,19 +54221,19 @@
       </c>
       <c r="M10" s="230">
         <f t="shared" si="1"/>
-        <v>9408.6959999999999</v>
+        <v>7011.5759999999991</v>
       </c>
       <c r="N10" s="286">
         <f>+'1'!N19+'2'!N19+'3'!N19+'4'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19+'11'!N19+'12'!N19+'13'!N19+'14'!N19+'15'!N19+'16'!N19+'17'!N19+'18'!N19+'19'!N19+'20'!N19+'21'!N19+'22'!N19+'23'!N19+'24'!N19+'25'!N19+'26'!N19+'27'!N19+'28'!N19+'29'!N19+'30'!N19</f>
-        <v>2155.4237288135591</v>
+        <v>1606.2711864406781</v>
       </c>
       <c r="O10" s="286">
         <f>+'1'!O19+'2'!O19+'3'!O19+'4'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19+'11'!O19+'12'!O19+'13'!O19+'14'!O19+'15'!O19+'16'!O19+'17'!O19+'18'!O19+'19'!O19+'20'!O19+'21'!O19+'22'!O19+'23'!O19+'24'!O19+'25'!O19+'26'!O19+'27'!O19+'28'!O19+'29'!O19+'30'!O19</f>
-        <v>57.820598644067793</v>
+        <v>43.089235932203387</v>
       </c>
       <c r="P10" s="119">
         <f t="shared" si="2"/>
-        <v>11621.940327457627</v>
+        <v>8660.9364223728808</v>
       </c>
       <c r="R10" s="299">
         <v>8</v>
@@ -54277,19 +54277,19 @@
       </c>
       <c r="H11" s="286">
         <f>+'1'!H20+'2'!H20+'3'!H20+'4'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20+'17'!H20+'18'!H20+'19'!H20+'20'!H20+'21'!H20+'22'!H20+'23'!H20+'24'!H20+'25'!H20+'26'!H20+'27'!H20+'28'!H20+'29'!H20+'30'!H20</f>
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="I11" s="236">
         <f t="shared" si="0"/>
-        <v>17433.599999999999</v>
+        <v>8716.7999999999993</v>
       </c>
       <c r="J11" s="286">
         <f>+'1'!J20+'2'!J20+'3'!J20+'4'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20+'19'!J20+'20'!J20+'21'!J20+'22'!J20+'23'!J20+'24'!J20+'25'!J20+'26'!J20+'27'!J20+'28'!J20+'29'!J20+'30'!J20</f>
-        <v>2440.7040000000002</v>
+        <v>1220.3520000000001</v>
       </c>
       <c r="K11" s="286">
         <f>+'1'!K20+'2'!K20+'3'!K20+'4'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20+'11'!K20+'12'!K20+'13'!K20+'14'!K20+'15'!K20+'16'!K20+'17'!K20+'18'!K20+'19'!K20+'20'!K20+'21'!K20+'22'!K20+'23'!K20+'24'!K20+'25'!K20+'26'!K20+'27'!K20+'28'!K20+'29'!K20+'30'!K20</f>
-        <v>508.48</v>
+        <v>203.39200000000002</v>
       </c>
       <c r="L11" s="286">
         <f>+'1'!L20+'2'!L20+'3'!L20+'4'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20+'11'!L20+'12'!L20+'13'!L20+'14'!L20+'15'!L20+'16'!L20+'17'!L20+'18'!L20+'19'!L20+'20'!L20+'21'!L20+'22'!L20+'23'!L20+'24'!L20+'25'!L20+'26'!L20+'27'!L20+'28'!L20+'29'!L20+'30'!L20</f>
@@ -54297,19 +54297,19 @@
       </c>
       <c r="M11" s="230">
         <f t="shared" si="1"/>
-        <v>14484.415999999997</v>
+        <v>7293.0559999999987</v>
       </c>
       <c r="N11" s="286">
         <f>+'1'!N20+'2'!N20+'3'!N20+'4'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20+'11'!N20+'12'!N20+'13'!N20+'14'!N20+'15'!N20+'16'!N20+'17'!N20+'18'!N20+'19'!N20+'20'!N20+'21'!N20+'22'!N20+'23'!N20+'24'!N20+'25'!N20+'26'!N20+'27'!N20+'28'!N20+'29'!N20+'30'!N20</f>
-        <v>3294.9152542372885</v>
+        <v>1647.4576271186443</v>
       </c>
       <c r="O11" s="286">
         <f>+'1'!O20+'2'!O20+'3'!O20+'4'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20+'11'!O20+'12'!O20+'13'!O20+'14'!O20+'15'!O20+'16'!O20+'17'!O20+'18'!O20+'19'!O20+'20'!O20+'21'!O20+'22'!O20+'23'!O20+'24'!O20+'25'!O20+'26'!O20+'27'!O20+'28'!O20+'29'!O20+'30'!O20</f>
-        <v>88.89665627118643</v>
+        <v>44.702568135593218</v>
       </c>
       <c r="P11" s="119">
         <f t="shared" si="2"/>
-        <v>17868.227910508474</v>
+        <v>8985.2161952542356</v>
       </c>
       <c r="R11" s="299">
         <v>9</v>
@@ -54353,19 +54353,19 @@
       </c>
       <c r="H12" s="286">
         <f>+'1'!H21+'2'!H21+'3'!H21+'4'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21+'17'!H21+'18'!H21+'19'!H21+'20'!H21+'21'!H21+'22'!H21+'23'!H21+'24'!H21+'25'!H21+'26'!H21+'27'!H21+'28'!H21+'29'!H21+'30'!H21</f>
-        <v>467</v>
+        <v>307</v>
       </c>
       <c r="I12" s="236">
         <f t="shared" si="0"/>
-        <v>33922.879999999997</v>
+        <v>22300.48</v>
       </c>
       <c r="J12" s="286">
         <f>+'1'!J21+'2'!J21+'3'!J21+'4'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21+'19'!J21+'20'!J21+'21'!J21+'22'!J21+'23'!J21+'24'!J21+'25'!J21+'26'!J21+'27'!J21+'28'!J21+'29'!J21+'30'!J21</f>
-        <v>4749.2032000000008</v>
+        <v>3122.0672000000004</v>
       </c>
       <c r="K12" s="286">
         <f>+'1'!K21+'2'!K21+'3'!K21+'4'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21+'11'!K21+'12'!K21+'13'!K21+'14'!K21+'15'!K21+'16'!K21+'17'!K21+'18'!K21+'19'!K21+'20'!K21+'21'!K21+'22'!K21+'23'!K21+'24'!K21+'25'!K21+'26'!K21+'27'!K21+'28'!K21+'29'!K21+'30'!K21</f>
-        <v>1187.3008000000002</v>
+        <v>780.5168000000001</v>
       </c>
       <c r="L12" s="286">
         <f>+'1'!L21+'2'!L21+'3'!L21+'4'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21+'11'!L21+'12'!L21+'13'!L21+'14'!L21+'15'!L21+'16'!L21+'17'!L21+'18'!L21+'19'!L21+'20'!L21+'21'!L21+'22'!L21+'23'!L21+'24'!L21+'25'!L21+'26'!L21+'27'!L21+'28'!L21+'29'!L21+'30'!L21</f>
@@ -54373,19 +54373,19 @@
       </c>
       <c r="M12" s="230">
         <f t="shared" si="1"/>
-        <v>27986.375999999997</v>
+        <v>18397.896000000001</v>
       </c>
       <c r="N12" s="286">
         <f>+'1'!N21+'2'!N21+'3'!N21+'4'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21+'11'!N21+'12'!N21+'13'!N21+'14'!N21+'15'!N21+'16'!N21+'17'!N21+'18'!N21+'19'!N21+'20'!N21+'21'!N21+'22'!N21+'23'!N21+'24'!N21+'25'!N21+'26'!N21+'27'!N21+'28'!N21+'29'!N21+'30'!N21</f>
-        <v>6411.3559322033907</v>
+        <v>4214.7457627118647</v>
       </c>
       <c r="O12" s="286">
         <f>+'1'!O21+'2'!O21+'3'!O21+'4'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21+'11'!O21+'12'!O21+'13'!O21+'14'!O21+'15'!O21+'16'!O21+'17'!O21+'18'!O21+'19'!O21+'20'!O21+'21'!O21+'22'!O21+'23'!O21+'24'!O21+'25'!O21+'26'!O21+'27'!O21+'28'!O21+'29'!O21+'30'!O21</f>
-        <v>171.98865966101692</v>
+        <v>113.06320881355931</v>
       </c>
       <c r="P12" s="119">
         <f t="shared" si="2"/>
-        <v>34569.720591864403</v>
+        <v>22725.704971525425</v>
       </c>
       <c r="R12" s="299">
         <v>10</v>
@@ -54645,19 +54645,19 @@
       </c>
       <c r="H16" s="113">
         <f t="shared" si="3"/>
-        <v>1273</v>
+        <v>713</v>
       </c>
       <c r="I16" s="114">
         <f t="shared" si="3"/>
-        <v>84218.122499999998</v>
+        <v>48382.322499999995</v>
       </c>
       <c r="J16" s="274">
         <f>SUM(J7:J15)</f>
-        <v>11790.53715</v>
+        <v>6773.5251500000004</v>
       </c>
       <c r="K16" s="275">
         <f t="shared" si="3"/>
-        <v>2845.9382875000001</v>
+        <v>1591.6852875000002</v>
       </c>
       <c r="L16" s="276">
         <f t="shared" si="3"/>
@@ -54665,19 +54665,19 @@
       </c>
       <c r="M16" s="232">
         <f t="shared" si="3"/>
-        <v>69581.647062499993</v>
+        <v>40017.112062499997</v>
       </c>
       <c r="N16" s="233">
         <f>SUM(N7:N15)</f>
-        <v>15917.033898305084</v>
+        <v>9144.1525423728817</v>
       </c>
       <c r="O16" s="101">
         <f>SUM(O7:O15)</f>
-        <v>427.49340480402537</v>
+        <v>245.80632302436442</v>
       </c>
       <c r="P16" s="234">
         <f>SUM(P7:P15)</f>
-        <v>85926.174365609098</v>
+        <v>49407.070927897243</v>
       </c>
       <c r="R16" s="299">
         <v>14</v>
@@ -54760,7 +54760,7 @@
       <c r="O19" s="366"/>
       <c r="P19" s="139">
         <f>I16</f>
-        <v>84218.122499999998</v>
+        <v>48382.322499999995</v>
       </c>
       <c r="R19" s="299">
         <v>17</v>
@@ -54792,7 +54792,7 @@
       <c r="O20" s="368"/>
       <c r="P20" s="140">
         <f>+J16</f>
-        <v>11790.53715</v>
+        <v>6773.5251500000004</v>
       </c>
       <c r="R20" s="299">
         <v>18</v>
@@ -54824,7 +54824,7 @@
       <c r="O21" s="368"/>
       <c r="P21" s="140">
         <f>+K16+L16</f>
-        <v>2845.9382875000001</v>
+        <v>1591.6852875000002</v>
       </c>
       <c r="R21" s="299">
         <v>19</v>
@@ -54857,7 +54857,7 @@
       <c r="O22" s="368"/>
       <c r="P22" s="140">
         <f>P19-P20-P21</f>
-        <v>69581.647062499993</v>
+        <v>40017.112062499997</v>
       </c>
       <c r="R22" s="299">
         <v>20</v>
@@ -54892,7 +54892,7 @@
       </c>
       <c r="P23" s="140">
         <f>+N16</f>
-        <v>15917.033898305084</v>
+        <v>9144.1525423728817</v>
       </c>
       <c r="R23" s="299">
         <v>21</v>
@@ -54925,7 +54925,7 @@
       <c r="O24" s="370"/>
       <c r="P24" s="140">
         <f>P22+P23</f>
-        <v>85498.680960805083</v>
+        <v>49161.264604872878</v>
       </c>
       <c r="R24" s="299">
         <v>22</v>
@@ -54961,7 +54961,7 @@
       </c>
       <c r="P25" s="140">
         <f>+O16</f>
-        <v>427.49340480402537</v>
+        <v>245.80632302436442</v>
       </c>
       <c r="R25" s="299">
         <v>23</v>
@@ -54982,7 +54982,7 @@
       <c r="O26" s="372"/>
       <c r="P26" s="297">
         <f>+P24+P25</f>
-        <v>85926.174365609113</v>
+        <v>49407.070927897243</v>
       </c>
       <c r="R26" s="299">
         <v>24</v>
@@ -55096,7 +55096,7 @@
       </c>
       <c r="T33" s="304">
         <f>SUM(T3:T32)</f>
-        <v>85926.174365609098</v>
+        <v>49407.070927897243</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.35">
@@ -55588,20 +55588,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>40</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>293.79000000000002</v>
+        <v>0</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>73.447500000000005</v>
+        <v>0</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -55609,19 +55607,19 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>1731.2625</v>
+        <v>0</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>10.639363347457627</v>
+        <v>0</v>
       </c>
       <c r="P16" s="310">
         <f>M16+N16+O16</f>
-        <v>2138.512032838983</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="313"/>
       <c r="S16" s="269">
@@ -55664,9 +55662,7 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>0</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
@@ -55741,20 +55737,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>40</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" ref="I18:I21" si="7">(G18*D18)*F18+H18*F18</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>293.79000000000002</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>73.447500000000005</v>
+        <v>0</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -55762,19 +55756,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>1731.2625</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>396.61016949152526</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>10.639363347457627</v>
+        <v>0</v>
       </c>
       <c r="P18" s="311">
         <f t="shared" si="5"/>
-        <v>2138.512032838983</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="156"/>
       <c r="S18" s="269">
@@ -55815,9 +55809,7 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>0</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -55888,20 +55880,18 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="306">
-        <v>80</v>
-      </c>
+      <c r="H20" s="306"/>
       <c r="I20" s="236">
         <f t="shared" si="7"/>
-        <v>5811.2</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>813.5680000000001</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>203.39200000000002</v>
+        <v>0</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -55909,19 +55899,19 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>4794.24</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>1098.3050847457628</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>29.462725423728813</v>
+        <v>0</v>
       </c>
       <c r="P20" s="311">
         <f t="shared" si="5"/>
-        <v>5922.0078101694908</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="314"/>
       <c r="S20" s="269">
@@ -55962,20 +55952,18 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>160</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="7"/>
-        <v>11622.4</v>
+        <v>0</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>1627.1360000000002</v>
+        <v>0</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>406.78400000000005</v>
+        <v>0</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -55983,19 +55971,19 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>9588.48</v>
+        <v>0</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>2196.6101694915255</v>
+        <v>0</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>58.925450847457626</v>
+        <v>0</v>
       </c>
       <c r="P21" s="311">
         <f t="shared" si="5"/>
-        <v>11844.015620338982</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="156"/>
       <c r="S21" s="269">
@@ -56250,19 +56238,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" ref="H25" si="9">SUM(H16:H24)</f>
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" ref="I25:M25" si="10">SUM(I16:I24)</f>
-        <v>21630.6</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>3028.2840000000006</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="10"/>
-        <v>757.07100000000014</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="10"/>
@@ -56270,19 +56258,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="10"/>
-        <v>17845.244999999999</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>4088.1355932203387</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>109.66690296610169</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>22043.047496186438</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="156"/>
     </row>
@@ -56333,7 +56321,7 @@
       <c r="O28" s="366"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>21630.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -56354,7 +56342,7 @@
       <c r="O29" s="368"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>3028.2840000000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -56375,7 +56363,7 @@
       <c r="O30" s="368"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>757.07100000000014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -56397,7 +56385,7 @@
       <c r="O31" s="368"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>17845.244999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -56421,7 +56409,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>4088.1355932203387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -56443,7 +56431,7 @@
       <c r="O33" s="370"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>21933.38059322034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -56468,7 +56456,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>109.6669029661017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -56478,7 +56466,7 @@
       <c r="O35" s="372"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>22043.047496186442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -57011,9 +56999,7 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>0</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
@@ -57087,9 +57073,7 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>0</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
@@ -57164,20 +57148,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>80</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>4197</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>587.58000000000004</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>146.89500000000001</v>
+        <v>0</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -57185,19 +57167,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>3462.5250000000001</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>793.22033898305051</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>21.278726694915253</v>
+        <v>0</v>
       </c>
       <c r="P18" s="311">
         <f t="shared" si="5"/>
-        <v>4277.0240656779661</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="156"/>
       <c r="S18" s="269">
@@ -57238,9 +57220,7 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>0</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -57311,9 +57291,7 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>0</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -57385,9 +57363,7 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>0</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -57673,19 +57649,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>4197</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>587.58000000000004</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>146.89500000000001</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -57693,19 +57669,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>3462.5250000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>793.22033898305051</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>21.278726694915253</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>4277.0240656779661</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="156"/>
     </row>
@@ -57756,7 +57732,7 @@
       <c r="O28" s="366"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>4197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -57777,7 +57753,7 @@
       <c r="O29" s="368"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>587.58000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -57798,7 +57774,7 @@
       <c r="O30" s="368"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>146.89500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -57820,7 +57796,7 @@
       <c r="O31" s="368"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>3462.5250000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -57844,7 +57820,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>793.22033898305051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -57866,7 +57842,7 @@
       <c r="O33" s="370"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>4255.7453389830507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -57891,7 +57867,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>21.278726694915253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -57901,7 +57877,7 @@
       <c r="O35" s="372"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>4277.0240656779661</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -58431,9 +58407,7 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112">
-        <v>0</v>
-      </c>
+      <c r="H16" s="112"/>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
         <v>0</v>
@@ -58507,9 +58481,7 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96">
-        <v>0</v>
-      </c>
+      <c r="H17" s="96"/>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
         <v>0</v>
@@ -58584,20 +58556,18 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96">
-        <v>80</v>
-      </c>
+      <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>4197</v>
+        <v>0</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>587.58000000000004</v>
+        <v>0</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>146.89500000000001</v>
+        <v>0</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -58605,19 +58575,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>3462.5250000000001</v>
+        <v>0</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>793.22033898305051</v>
+        <v>0</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>21.278726694915253</v>
+        <v>0</v>
       </c>
       <c r="P18" s="311">
         <f t="shared" si="5"/>
-        <v>4277.0240656779661</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="156"/>
       <c r="S18" s="269">
@@ -58658,20 +58628,18 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96">
-        <v>40</v>
-      </c>
+      <c r="H19" s="96"/>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>406.78400000000005</v>
+        <v>0</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>101.69600000000001</v>
+        <v>0</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -58679,19 +58647,19 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2397.12</v>
+        <v>0</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>14.731362711864406</v>
+        <v>0</v>
       </c>
       <c r="P19" s="311">
         <f t="shared" si="5"/>
-        <v>2961.0039050847454</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="156"/>
       <c r="S19" s="269">
@@ -58731,20 +58699,18 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96">
-        <v>40</v>
-      </c>
+      <c r="H20" s="96"/>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>0</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>406.78400000000005</v>
+        <v>0</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>101.69600000000001</v>
+        <v>0</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -58752,19 +58718,19 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>2397.12</v>
+        <v>0</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>549.15254237288138</v>
+        <v>0</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>14.731362711864406</v>
+        <v>0</v>
       </c>
       <c r="P20" s="311">
         <f t="shared" si="5"/>
-        <v>2961.0039050847454</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="156"/>
       <c r="S20" s="269">
@@ -58805,9 +58771,7 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96">
-        <v>0</v>
-      </c>
+      <c r="H21" s="96"/>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -59093,19 +59057,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>10008.200000000001</v>
+        <v>0</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>1401.1480000000001</v>
+        <v>0</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>350.28700000000003</v>
+        <v>0</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -59113,19 +59077,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>8256.7649999999994</v>
+        <v>0</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>1891.5254237288132</v>
+        <v>0</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>50.741452118644062</v>
+        <v>0</v>
       </c>
       <c r="P25" s="113">
         <f>SUM(P16:P24)</f>
-        <v>10199.031875847457</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="156"/>
     </row>
@@ -59176,7 +59140,7 @@
       <c r="O28" s="366"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>10008.200000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -59197,7 +59161,7 @@
       <c r="O29" s="368"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>1401.1480000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -59218,7 +59182,7 @@
       <c r="O30" s="368"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>350.28700000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -59240,7 +59204,7 @@
       <c r="O31" s="368"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>8256.7649999999994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -59264,7 +59228,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>1891.5254237288132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -59286,7 +59250,7 @@
       <c r="O33" s="370"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>10148.290423728813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -59311,7 +59275,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>50.741452118644069</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -59321,7 +59285,7 @@
       <c r="O35" s="372"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>10199.031875847457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
